--- a/results_v3/tables/table2_difficulty.xlsx
+++ b/results_v3/tables/table2_difficulty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,109 +567,220 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>POMCP (known model)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.48±0.08</t>
+          <t>1.00±0.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.66±0.69</t>
+          <t>2.46±0.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33±0.05</t>
+          <t>0.91±0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.67±1.03</t>
+          <t>5.79±0.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.13±0.04</t>
+          <t>0.17±0.01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.06±1.64</t>
+          <t>10.10±0.28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DQN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.47±0.11</t>
+          <t>0.48±0.08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.51±2.69</t>
+          <t>5.66±0.69</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.30±0.03</t>
+          <t>0.33±0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.34±2.27</t>
+          <t>6.67±1.03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.11±0.02</t>
+          <t>0.13±0.04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.42±1.67</t>
+          <t>5.06±1.64</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.47±0.11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.51±2.69</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.30±0.03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>11.34±2.27</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.11±0.02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>11.42±1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DQN-GRU (memory)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.82±0.12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.17±1.41</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.45±0.05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9.03±0.80</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.10±0.03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8.49±2.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO-Stack (memory)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.45±0.13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.46±1.25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.34±0.07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6.64±1.16</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.13±0.05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5.90±1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MuZero (ours)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0.72±0.08</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>6.51±1.45</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.68±0.04</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>8.94±0.81</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>0.28±0.06</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>10.00±0.92</t>
         </is>
